--- a/PCB Lattice/V3/BOM PPU_LITE_LATT_V3.xlsx
+++ b/PCB Lattice/V3/BOM PPU_LITE_LATT_V3.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="114">
   <si>
     <t>U3</t>
   </si>
@@ -352,6 +352,12 @@
   </si>
   <si>
     <t>SO-20-200</t>
+  </si>
+  <si>
+    <t>SN74LVC1G17DBVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  SOT-23-5</t>
   </si>
 </sst>
 </file>
@@ -361,7 +367,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="47" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -700,6 +706,13 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="24">
     <fill>
@@ -819,7 +832,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -931,6 +944,15 @@
       </top>
       <bottom style="thin">
         <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE5E5E5"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2519,7 +2541,7 @@
     <xf numFmtId="0" fontId="42" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="42" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2599,6 +2621,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1573">
@@ -4473,7 +4498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:U50"/>
+  <dimension ref="A4:U51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -4718,125 +4743,113 @@
       <c r="I12" s="20"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="30" t="s">
-        <v>72</v>
+      <c r="E13" s="20" t="s">
+        <v>112</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" s="20"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>88</v>
+      <c r="E14" s="30" t="s">
+        <v>72</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1206</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>87</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="30" t="s">
-        <v>13</v>
+      <c r="E15" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1206</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>103</v>
+      <c r="E16" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="19"/>
+        <v>29</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>75</v>
+      </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
@@ -4858,16 +4871,16 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="7"/>
@@ -4891,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>31</v>
@@ -4900,7 +4913,7 @@
         <v>24</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I18" s="19"/>
       <c r="J18" s="7"/>
@@ -4924,16 +4937,16 @@
         <v>1</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="7"/>
@@ -4950,13 +4963,14 @@
       <c r="U19" s="7"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>31</v>
@@ -4965,38 +4979,39 @@
         <v>15</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I20" s="6"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
+        <v>104</v>
+      </c>
+      <c r="I20" s="19"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>94</v>
+        <v>15</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="9"/>
@@ -5013,49 +5028,47 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="C22" s="1"/>
       <c r="D22" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>48</v>
+        <v>24</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="I22" s="6"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D23" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>31</v>
@@ -5064,7 +5077,7 @@
         <v>15</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="5"/>
@@ -5082,13 +5095,13 @@
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>31</v>
@@ -5097,7 +5110,7 @@
         <v>15</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="5"/>
@@ -5111,15 +5124,27 @@
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
     </row>
-    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="5"/>
+      <c r="C25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="I25" s="6"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -5132,26 +5157,15 @@
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>42</v>
-      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="5"/>
       <c r="I26" s="6"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -5166,21 +5180,23 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="C27" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="D27" s="1">
         <v>2</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="5"/>
@@ -5201,7 +5217,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>58</v>
@@ -5210,11 +5226,9 @@
         <v>57</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>92</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="I28" s="6"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
@@ -5230,10 +5244,10 @@
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>58</v>
@@ -5242,9 +5256,11 @@
         <v>57</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I29" s="6"/>
+        <v>56</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
@@ -5260,10 +5276,10 @@
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>58</v>
@@ -5272,7 +5288,7 @@
         <v>57</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="5"/>
@@ -5290,19 +5306,19 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" s="5"/>
@@ -5323,16 +5339,16 @@
         <v>3</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="5"/>
@@ -5353,16 +5369,16 @@
         <v>3</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="5"/>
@@ -5376,57 +5392,56 @@
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
     </row>
-    <row r="34" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
-      <c r="C34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>39</v>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G34" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I34" s="13"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
+      <c r="H34" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I34" s="6"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
     </row>
     <row r="35" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E35" s="25" t="s">
-        <v>95</v>
+      <c r="C35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>39</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>96</v>
+        <v>30</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="3"/>
@@ -5440,13 +5455,15 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C36" s="7"/>
+    <row r="36" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
       <c r="D36" s="5" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>79</v>
@@ -5455,20 +5472,19 @@
         <v>53</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I36" s="12"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="I36" s="13"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C37" s="7"/>
@@ -5476,14 +5492,16 @@
         <v>25</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G37" s="5"/>
+        <v>79</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="H37" s="7" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="4"/>
@@ -5499,87 +5517,84 @@
       <c r="T37" s="4"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C38" s="24"/>
+      <c r="C38" s="7"/>
       <c r="D38" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>53</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G38" s="5"/>
       <c r="H38" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="7"/>
-      <c r="S38" s="7"/>
+        <v>97</v>
+      </c>
+      <c r="I38" s="12"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
       <c r="T38" s="4"/>
     </row>
-    <row r="39" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="C39" s="24" t="s">
-        <v>32</v>
-      </c>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C39" s="24"/>
       <c r="D39" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>34</v>
+      <c r="E39" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="I39" s="6"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="U39" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I39" s="19"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="4"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
+      <c r="C40" s="24" t="s">
+        <v>32</v>
+      </c>
       <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I40" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="I40" s="6"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
@@ -5595,11 +5610,21 @@
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
+      <c r="D41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
@@ -5635,9 +5660,11 @@
       <c r="U42" s="2"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
       <c r="D43" s="5"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="22"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="23"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -5655,8 +5682,8 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="23"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="22"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -5689,88 +5716,87 @@
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
       <c r="S45" s="5"/>
+      <c r="U45" s="2"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3"/>
-      <c r="S46" s="3"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C47" s="4"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+      <c r="S47" s="3"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C48" s="4"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="7"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
       <c r="T48" s="4"/>
     </row>
     <row r="49" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7"/>
+      <c r="S49" s="7"/>
       <c r="T49" s="4"/>
     </row>
     <row r="50" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C50" s="4"/>
-      <c r="D50" s="7"/>
+      <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
@@ -5787,6 +5813,26 @@
       <c r="R50" s="4"/>
       <c r="S50" s="4"/>
       <c r="T50" s="4"/>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C51" s="4"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PCB Lattice/V3/BOM PPU_LITE_LATT_V3.xlsx
+++ b/PCB Lattice/V3/BOM PPU_LITE_LATT_V3.xlsx
@@ -327,15 +327,9 @@
     <t xml:space="preserve">10kΩ±5%    </t>
   </si>
   <si>
-    <t xml:space="preserve">39kΩ±5%    </t>
-  </si>
-  <si>
     <t>RC0805JR-0710KL</t>
   </si>
   <si>
-    <t>RC0805JR-0739KL</t>
-  </si>
-  <si>
     <t xml:space="preserve">12kΩ±5%    </t>
   </si>
   <si>
@@ -358,6 +352,12 @@
   </si>
   <si>
     <t xml:space="preserve">  SOT-23-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,1kΩ±5%    </t>
+  </si>
+  <si>
+    <t>RC0805JR-079K1L</t>
   </si>
 </sst>
 </file>
@@ -4663,16 +4663,16 @@
         <v>1</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="9"/>
@@ -4750,16 +4750,16 @@
         <v>1</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="32" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="7"/>
@@ -4871,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>31</v>
@@ -4880,7 +4880,7 @@
         <v>15</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="7"/>
@@ -4904,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>31</v>
@@ -4913,7 +4913,7 @@
         <v>24</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I18" s="19"/>
       <c r="J18" s="7"/>
@@ -4937,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>31</v>
@@ -4946,7 +4946,7 @@
         <v>24</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="7"/>
@@ -4979,7 +4979,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I20" s="19"/>
       <c r="J20" s="7"/>

--- a/PCB Lattice/V3/BOM PPU_LITE_LATT_V3.xlsx
+++ b/PCB Lattice/V3/BOM PPU_LITE_LATT_V3.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="112">
   <si>
     <t>U3</t>
   </si>
@@ -178,12 +178,6 @@
   </si>
   <si>
     <t>1210</t>
-  </si>
-  <si>
-    <t>GRM32ER71E226ME15L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22uFX7R 50V 10% </t>
   </si>
   <si>
     <t>CAT16-101J4LF</t>
@@ -4498,7 +4492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:U51"/>
+  <dimension ref="A4:U50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -4663,16 +4657,16 @@
         <v>1</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="9"/>
@@ -4717,19 +4711,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G11" s="27" t="s">
         <v>52</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
@@ -4750,16 +4744,16 @@
         <v>1</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="7"/>
@@ -4774,19 +4768,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
@@ -4811,19 +4805,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G15" s="3">
         <v>1206</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -4848,7 +4842,7 @@
         <v>13</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -4871,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>31</v>
@@ -4880,7 +4874,7 @@
         <v>15</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="7"/>
@@ -4904,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>31</v>
@@ -4913,7 +4907,7 @@
         <v>24</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I18" s="19"/>
       <c r="J18" s="7"/>
@@ -4937,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>31</v>
@@ -4946,7 +4940,7 @@
         <v>24</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="7"/>
@@ -4970,7 +4964,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>31</v>
@@ -4979,7 +4973,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I20" s="19"/>
       <c r="J20" s="7"/>
@@ -5002,7 +4996,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>31</v>
@@ -5011,7 +5005,7 @@
         <v>15</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="9"/>
@@ -5033,7 +5027,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>31</v>
@@ -5042,7 +5036,7 @@
         <v>24</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="9"/>
@@ -5217,16 +5211,16 @@
         <v>2</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="5"/>
@@ -5247,19 +5241,19 @@
         <v>2</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -5279,16 +5273,16 @@
         <v>4</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="5"/>
@@ -5309,16 +5303,16 @@
         <v>8</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" s="5"/>
@@ -5339,7 +5333,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>31</v>
@@ -5348,7 +5342,7 @@
         <v>24</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="5"/>
@@ -5369,16 +5363,16 @@
         <v>3</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="5"/>
@@ -5399,16 +5393,16 @@
         <v>3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="5"/>
@@ -5429,7 +5423,7 @@
         <v>26</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>39</v>
@@ -5460,19 +5454,19 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>53</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="3"/>
@@ -5492,16 +5486,16 @@
         <v>25</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>53</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="4"/>
@@ -5522,14 +5516,14 @@
         <v>25</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="4"/>
@@ -5544,57 +5538,58 @@
       <c r="S38" s="4"/>
       <c r="T38" s="4"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C39" s="24"/>
+    <row r="39" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="C39" s="24" t="s">
+        <v>32</v>
+      </c>
       <c r="D39" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E39" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>30</v>
+      <c r="E39" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="7"/>
-      <c r="T39" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="6"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="U39" s="2"/>
     </row>
-    <row r="40" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="C40" s="24" t="s">
-        <v>32</v>
-      </c>
+      <c r="B40" s="1"/>
       <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H40" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="I40" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
@@ -5610,21 +5605,11 @@
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="D41" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>84</v>
-      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
@@ -5660,11 +5645,9 @@
       <c r="U42" s="2"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
       <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="23"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="22"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -5682,8 +5665,8 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D44" s="5"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="22"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="23"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -5716,87 +5699,88 @@
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
       <c r="S45" s="5"/>
-      <c r="U45" s="2"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="5"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-      <c r="S47" s="3"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C48" s="4"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="7"/>
+      <c r="S48" s="7"/>
       <c r="T48" s="4"/>
     </row>
     <row r="49" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C49" s="4"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="7"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
       <c r="T49" s="4"/>
     </row>
     <row r="50" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
+      <c r="D50" s="7"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
@@ -5813,26 +5797,6 @@
       <c r="R50" s="4"/>
       <c r="S50" s="4"/>
       <c r="T50" s="4"/>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C51" s="4"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
